--- a/Tests/XLSXTest/Resources/simple.xlsx
+++ b/Tests/XLSXTest/Resources/simple.xlsx
@@ -35,17 +35,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>